--- a/Fase 2/Evidencias Proyecto/Evidencias de documentación/2.3 Plan de Pruebas/Matriz de trazabilidad de Pruebas.xlsx
+++ b/Fase 2/Evidencias Proyecto/Evidencias de documentación/2.3 Plan de Pruebas/Matriz de trazabilidad de Pruebas.xlsx
@@ -1710,8 +1710,10 @@
       <c r="C35" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="D35" s="5" t="s">
-        <v>262</v>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Usuarios principal, apadrinado, soporte (rol SOPORTE) y administrador; operaciones permitidas y prohibidas.</t>
+        </is>
       </c>
       <c r="E35" s="5" t="s">
         <v>263</v>
